--- a/SKU_Inventory_Audit_Workbook.xlsx
+++ b/SKU_Inventory_Audit_Workbook.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="440">
   <si>
     <t xml:space="preserve">SKU Inventory Audit Workbook — Scan Log</t>
   </si>
@@ -566,6 +566,27 @@
   </si>
   <si>
     <t xml:space="preserve">Private Sub Worksheet_Change(ByVal Target As Range)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Scan Date and Auditor Initials depend on iterative calculation, which some</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Excel save/round-trip paths (e.g. Save As Macro-Enabled Workbook) can reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' even though it's saved in the file. Force it on every time this runs, so a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' lost setting can't silently break the freeze-on-first-entry formulas again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Application.Iteration = True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Application.MaxIterations = 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Application.MaxChange = 0.001</t>
   </si>
   <si>
     <t xml:space="preserve">    Dim pasteRange As Range, countRange As Range</t>
@@ -24649,7 +24670,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A377"/>
+  <dimension ref="A1:A385"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
@@ -24784,26 +24805,28 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29"/>
+      <c r="A30" s="29" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24811,18 +24834,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29" t="s">
-        <v>189</v>
-      </c>
+      <c r="A38" s="29"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
@@ -24845,38 +24866,36 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="29" t="s">
-        <v>194</v>
-      </c>
+      <c r="A43" s="29"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="29" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24886,124 +24905,126 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="29" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="29" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="29" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="29"/>
+      <c r="A57" s="29" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="29" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="29"/>
+      <c r="A59" s="29" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="29"/>
+      <c r="A60" s="29" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="29" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="29"/>
+      <c r="A62" s="29" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="29" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="29" t="s">
-        <v>208</v>
-      </c>
+      <c r="A65" s="29"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="29"/>
+      <c r="A66" s="29" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="29" t="s">
-        <v>209</v>
-      </c>
+      <c r="A67" s="29"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="29" t="s">
-        <v>210</v>
-      </c>
+      <c r="A68" s="29"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="29"/>
+      <c r="A69" s="29" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="29" t="s">
-        <v>211</v>
-      </c>
+      <c r="A70" s="29"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="29" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="29" t="s">
-        <v>215</v>
-      </c>
+      <c r="A74" s="29"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="29"/>
+      <c r="A75" s="29" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="29" t="s">
-        <v>217</v>
-      </c>
+      <c r="A77" s="29"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="29" t="s">
@@ -25031,97 +25052,97 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="29" t="s">
-        <v>223</v>
-      </c>
+      <c r="A83" s="29"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="29" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="29" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="29" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="29" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="29"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="29" t="s">
@@ -25159,42 +25180,42 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="29" t="s">
-        <v>248</v>
-      </c>
+      <c r="A109" s="29"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="29" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="29" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="29" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="29"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="29" t="s">
@@ -25212,27 +25233,27 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="29"/>
+      <c r="A120" s="29" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="29" t="s">
-        <v>261</v>
-      </c>
+      <c r="A124" s="29"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="29" t="s">
@@ -25240,17 +25261,17 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="29"/>
+      <c r="A126" s="29" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="29" t="s">
-        <v>264</v>
-      </c>
+      <c r="A128" s="29"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="29" t="s">
@@ -25268,11 +25289,13 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="29"/>
+      <c r="A132" s="29" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25280,35 +25303,35 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="29" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="29"/>
+      <c r="A138" s="29" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="29" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="29" t="s">
-        <v>272</v>
-      </c>
+      <c r="A140" s="29"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="29" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25316,37 +25339,35 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="29" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="29" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="29" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="29" t="s">
-        <v>276</v>
-      </c>
+      <c r="A146" s="29"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="29" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="29" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="29" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25388,12 +25409,12 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="29" t="s">
+      <c r="A158" s="29"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="29" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="29"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="29" t="s">
@@ -25427,7 +25448,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="29" t="s">
-        <v>203</v>
+        <v>294</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25435,113 +25456,115 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="29" t="s">
-        <v>204</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="29"/>
+      <c r="A169" s="29" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="29"/>
+      <c r="A170" s="29" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="29" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="29" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="29" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="29" t="s">
-        <v>297</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="29" t="s">
-        <v>298</v>
-      </c>
+      <c r="A175" s="29"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="29"/>
+      <c r="A176" s="29" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="29" t="s">
-        <v>299</v>
-      </c>
+      <c r="A177" s="29"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="29"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="29" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="29"/>
+      <c r="A182" s="29" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="29" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="29" t="s">
-        <v>304</v>
-      </c>
+      <c r="A184" s="29"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="29"/>
+      <c r="A185" s="29" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="29" t="s">
-        <v>305</v>
-      </c>
+      <c r="A186" s="29"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="29"/>
+      <c r="A187" s="29" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="29" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="29" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="29" t="s">
-        <v>308</v>
-      </c>
+      <c r="A190" s="29"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="29" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="29" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25549,41 +25572,39 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="29" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="29" t="s">
-        <v>311</v>
-      </c>
+      <c r="A195" s="29"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="29"/>
+      <c r="A198" s="29" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="29" t="s">
-        <v>315</v>
+        <v>210</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="29" t="s">
-        <v>316</v>
-      </c>
+      <c r="A201" s="29"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="29" t="s">
@@ -25592,103 +25613,101 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="29" t="s">
-        <v>203</v>
+        <v>318</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="29"/>
+      <c r="A204" s="29" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="29" t="s">
-        <v>319</v>
-      </c>
+      <c r="A206" s="29"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="29" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="29" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="29" t="s">
-        <v>203</v>
+        <v>323</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="29"/>
+      <c r="A210" s="29" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="29" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="29"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="29"/>
+      <c r="A213" s="29" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="29" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="29"/>
+      <c r="A216" s="29" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="29" t="s">
-        <v>323</v>
+        <v>210</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="29" t="s">
-        <v>324</v>
-      </c>
+      <c r="A218" s="29"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="29" t="s">
-        <v>325</v>
+        <v>211</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="29" t="s">
-        <v>326</v>
-      </c>
+      <c r="A220" s="29"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="29" t="s">
-        <v>279</v>
-      </c>
+      <c r="A221" s="29"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="29" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="29" t="s">
-        <v>329</v>
-      </c>
+      <c r="A224" s="29"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="29" t="s">
@@ -25697,49 +25716,51 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="29" t="s">
-        <v>203</v>
+        <v>331</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="29"/>
+      <c r="A227" s="29" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="29" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="29" t="s">
-        <v>332</v>
+        <v>286</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="29" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="29"/>
+      <c r="A232" s="29" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="29" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="29" t="s">
-        <v>336</v>
+        <v>210</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="29" t="s">
-        <v>337</v>
-      </c>
+      <c r="A235" s="29"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="29" t="s">
@@ -25762,108 +25783,108 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="29" t="s">
-        <v>342</v>
-      </c>
+      <c r="A240" s="29"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="29" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="29" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="29" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="29"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="29" t="s">
-        <v>204</v>
+        <v>345</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="29"/>
+      <c r="A245" s="29" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="29"/>
+      <c r="A246" s="29" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="29" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="29" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="29" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="29" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="29" t="s">
-        <v>349</v>
-      </c>
+      <c r="A251" s="29"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="29"/>
+      <c r="A252" s="29" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="29" t="s">
-        <v>323</v>
-      </c>
+      <c r="A253" s="29"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="29" t="s">
-        <v>324</v>
-      </c>
+      <c r="A254" s="29"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="29" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="29" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="29" t="s">
-        <v>355</v>
-      </c>
+      <c r="A260" s="29"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="29"/>
+      <c r="A261" s="29" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="29" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25892,12 +25913,12 @@
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="29"/>
+      <c r="A268" s="29" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="29" t="s">
-        <v>362</v>
-      </c>
+      <c r="A269" s="29"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="29" t="s">
@@ -25930,76 +25951,76 @@
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="29" t="s">
-        <v>240</v>
-      </c>
+      <c r="A276" s="29"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="29" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="29" t="s">
-        <v>278</v>
+        <v>370</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="29" t="s">
-        <v>279</v>
+        <v>371</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="29"/>
+      <c r="A280" s="29" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="29" t="s">
-        <v>204</v>
+        <v>373</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="29"/>
+      <c r="A282" s="29" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="29"/>
+      <c r="A283" s="29" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="29" t="s">
-        <v>369</v>
+        <v>247</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="29" t="s">
-        <v>370</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="29" t="s">
-        <v>371</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="29"/>
+      <c r="A287" s="29" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="29" t="s">
-        <v>372</v>
-      </c>
+      <c r="A288" s="29"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="29" t="s">
-        <v>373</v>
+        <v>211</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="29" t="s">
-        <v>374</v>
-      </c>
+      <c r="A290" s="29"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="29" t="s">
-        <v>375</v>
-      </c>
+      <c r="A291" s="29"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="29" t="s">
@@ -26017,9 +26038,7 @@
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="29" t="s">
-        <v>278</v>
-      </c>
+      <c r="A295" s="29"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="29" t="s">
@@ -26027,97 +26046,99 @@
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="29"/>
+      <c r="A297" s="29" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="29" t="s">
-        <v>204</v>
+        <v>381</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="29"/>
+      <c r="A299" s="29" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="29"/>
+      <c r="A300" s="29" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="29" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="29" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="29" t="s">
-        <v>382</v>
+        <v>285</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="29" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="29" t="s">
-        <v>384</v>
-      </c>
+      <c r="A305" s="29"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="29" t="s">
-        <v>385</v>
+        <v>211</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="29"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="29" t="s">
-        <v>386</v>
-      </c>
+      <c r="A308" s="29"/>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="29"/>
+      <c r="A309" s="29" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="29" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="29"/>
+      <c r="A312" s="29" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="29" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="29" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="29" t="s">
-        <v>391</v>
-      </c>
+      <c r="A315" s="29"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="29" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="29" t="s">
-        <v>393</v>
-      </c>
+      <c r="A317" s="29"/>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="29" t="s">
@@ -26130,18 +26151,16 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="29" t="s">
-        <v>396</v>
-      </c>
+      <c r="A320" s="29"/>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="29" t="s">
-        <v>238</v>
+        <v>397</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26151,64 +26170,66 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="29" t="s">
-        <v>240</v>
+        <v>399</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="29" t="s">
-        <v>277</v>
+        <v>400</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="29" t="s">
-        <v>278</v>
+        <v>401</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="29" t="s">
-        <v>279</v>
+        <v>402</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="29"/>
+      <c r="A328" s="29" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="29" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="29"/>
+      <c r="A330" s="29" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="29" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="29" t="s">
-        <v>401</v>
+        <v>247</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="29" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="29" t="s">
-        <v>403</v>
+        <v>285</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="29" t="s">
-        <v>404</v>
+        <v>286</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="29" t="s">
-        <v>405</v>
-      </c>
+      <c r="A336" s="29"/>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="29" t="s">
@@ -26216,188 +26237,226 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="29" t="s">
-        <v>407</v>
-      </c>
+      <c r="A338" s="29"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="29" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="29" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="29" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="29" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="29" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="29" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="29" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="29" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="29" t="s">
-        <v>277</v>
+        <v>418</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="29" t="s">
-        <v>278</v>
+        <v>419</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="29"/>
+      <c r="A353" s="29" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="29" t="s">
-        <v>285</v>
+        <v>422</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="29"/>
+      <c r="A355" s="29" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="29" t="s">
-        <v>204</v>
+        <v>424</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="29"/>
+      <c r="A357" s="29" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="29"/>
+      <c r="A358" s="29" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="29" t="s">
-        <v>420</v>
+        <v>285</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="29"/>
+      <c r="A360" s="29" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="29" t="s">
-        <v>421</v>
-      </c>
+      <c r="A361" s="29"/>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="29" t="s">
-        <v>422</v>
+        <v>292</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="29" t="s">
-        <v>423</v>
-      </c>
+      <c r="A363" s="29"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="29" t="s">
-        <v>424</v>
+        <v>211</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="29"/>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="29" t="s">
-        <v>338</v>
-      </c>
+      <c r="A366" s="29"/>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="29" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="29" t="s">
-        <v>426</v>
-      </c>
+      <c r="A368" s="29"/>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="29" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="29" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="29" t="s">
-        <v>431</v>
-      </c>
+      <c r="A373" s="29"/>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="29" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="29"/>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="29" t="s">
-        <v>204</v>
+        <v>433</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="29"/>
+      <c r="A377" s="29" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="29" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="29" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="29" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="29" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="29" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="29"/>
+    </row>
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
